--- a/KMS/KMS_MATERIAL_PRICES.xlsx
+++ b/KMS/KMS_MATERIAL_PRICES.xlsx
@@ -28,9 +28,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy hh:mm"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -652,11 +651,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SE-7154</t>
+          <t>SE-2610</t>
         </is>
       </c>
       <c r="J2" s="7" t="n">
-        <v>46287.604007416</v>
+        <v>46287.62223733011</v>
       </c>
     </row>
     <row r="3">
@@ -681,24 +680,24 @@
         </is>
       </c>
       <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SE-6849</t>
+          <t>SE-3114</t>
         </is>
       </c>
       <c r="J3" s="7" t="n">
-        <v>46287.60400294705</v>
+        <v>46287.62223950878</v>
       </c>
     </row>
     <row r="4">
@@ -740,7 +739,7 @@
         </is>
       </c>
       <c r="J4" s="7" t="n">
-        <v>46287.60400294744</v>
+        <v>46287.60400295139</v>
       </c>
     </row>
     <row r="5">
@@ -773,7 +772,7 @@
         </is>
       </c>
       <c r="J5" s="7" t="n">
-        <v>46287.60400294772</v>
+        <v>46287.60400295139</v>
       </c>
     </row>
     <row r="6">
@@ -802,11 +801,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SE-7066</t>
+          <t>SE-3114</t>
         </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>46287.60400585963</v>
+        <v>46287.62223950917</v>
       </c>
     </row>
     <row r="7">
@@ -848,7 +847,7 @@
         </is>
       </c>
       <c r="J7" s="7" t="n">
-        <v>46287.60400585997</v>
+        <v>46287.60400585648</v>
       </c>
     </row>
     <row r="8">
@@ -877,11 +876,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SE-7066</t>
+          <t>SE-3114</t>
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>46287.60400586032</v>
+        <v>46287.62223950831</v>
       </c>
     </row>
     <row r="9">
@@ -906,24 +905,24 @@
         </is>
       </c>
       <c r="E9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" t="n">
-        <v>5.6</v>
-      </c>
       <c r="G9" t="n">
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.2857142857142858</v>
+        <v>0.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SE-7066</t>
+          <t>SE-2610</t>
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>46287.60400586045</v>
+        <v>46287.62223732909</v>
       </c>
     </row>
     <row r="10">
@@ -956,7 +955,7 @@
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>46287.60398653874</v>
+        <v>46287.6222373303</v>
       </c>
     </row>
     <row r="11">
@@ -985,11 +984,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SE-3999</t>
+          <t>SE-3114</t>
         </is>
       </c>
       <c r="J11" s="7" t="n">
-        <v>46287.60399174483</v>
+        <v>46287.62223950864</v>
       </c>
     </row>
     <row r="12">
@@ -1022,7 +1021,7 @@
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>46287.60400030691</v>
+        <v>46287.6040003125</v>
       </c>
     </row>
     <row r="13">
@@ -1055,7 +1054,7 @@
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>46287.60399839914</v>
+        <v>46287.60399840278</v>
       </c>
     </row>
     <row r="14">
@@ -1088,7 +1087,7 @@
         </is>
       </c>
       <c r="J14" s="7" t="n">
-        <v>46287.60399839903</v>
+        <v>46287.60399840278</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3285,6 +3284,72 @@
       <c r="G61" t="inlineStr">
         <is>
           <t>SE-7066</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KMS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>017-5907758511244</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025 ORANGE DUCT TAPE - ROUGH SURFACE -48mm x 50m-Commodity code: 39191019 country of origin - Poland</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SE-2610</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>KMS</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>208-SPARE WIRE-1.5m</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SPARE HOT WIRE 1.5m</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SE-3114</t>
         </is>
       </c>
     </row>
